--- a/data_lake/industry/CFM/OEM SSD.xlsx
+++ b/data_lake/industry/CFM/OEM SSD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/CFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2015A89E-3587-4366-854A-5F4D2B154DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5E60DE-F67D-7F43-AA31-50B478FCEFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18220" yWindow="780" windowWidth="17780" windowHeight="20760" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OEM SSD 256GB SATA" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -75,30 +75,30 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -136,50 +136,50 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -457,20 +457,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -516,7 +516,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -539,7 +539,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -562,7 +562,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -585,7 +585,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -608,7 +608,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -631,7 +631,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -654,7 +654,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -677,7 +677,7 @@
         <v>18.2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -700,7 +700,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -723,7 +723,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -746,7 +746,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -769,7 +769,7 @@
         <v>20.399999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -792,7 +792,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -815,7 +815,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -838,7 +838,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -861,7 +861,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -884,7 +884,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -907,7 +907,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -930,7 +930,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -953,7 +953,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -976,7 +976,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -999,7 +999,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -1091,7 +1091,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -1137,7 +1137,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -1183,7 +1183,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -1206,7 +1206,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -1229,7 +1229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -1436,7 +1436,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -1597,7 +1597,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -1643,7 +1643,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -1687,6 +1687,167 @@
       </c>
       <c r="G53" s="9">
         <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>67</v>
+      </c>
+      <c r="F54" s="9">
+        <v>71</v>
+      </c>
+      <c r="G54" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>67</v>
+      </c>
+      <c r="F55" s="9">
+        <v>71</v>
+      </c>
+      <c r="G55" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>67</v>
+      </c>
+      <c r="F56" s="9">
+        <v>71</v>
+      </c>
+      <c r="G56" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>67</v>
+      </c>
+      <c r="F57" s="9">
+        <v>71</v>
+      </c>
+      <c r="G57" s="9">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>64</v>
+      </c>
+      <c r="F58" s="9">
+        <v>68</v>
+      </c>
+      <c r="G58" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>64</v>
+      </c>
+      <c r="F59" s="9">
+        <v>68</v>
+      </c>
+      <c r="G59" s="9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>64</v>
+      </c>
+      <c r="F60" s="9">
+        <v>68</v>
+      </c>
+      <c r="G60" s="9">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1697,19 +1858,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F473D36E-208F-4614-83B5-69AB6F33294E}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1732,7 +1893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -1755,7 +1916,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -1778,7 +1939,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -1801,7 +1962,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -1824,7 +1985,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -1847,7 +2008,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -1870,7 +2031,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -1893,7 +2054,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -1916,7 +2077,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -1939,7 +2100,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -1962,7 +2123,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -1985,7 +2146,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -2008,7 +2169,7 @@
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -2031,7 +2192,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -2054,7 +2215,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -2077,7 +2238,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -2100,7 +2261,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -2123,7 +2284,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -2146,7 +2307,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -2169,7 +2330,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -2192,7 +2353,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -2215,7 +2376,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -2238,7 +2399,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -2261,7 +2422,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -2284,7 +2445,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -2307,7 +2468,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -2330,7 +2491,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -2353,7 +2514,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -2376,7 +2537,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -2399,7 +2560,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -2422,7 +2583,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -2445,7 +2606,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -2468,7 +2629,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -2491,7 +2652,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -2514,7 +2675,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -2537,7 +2698,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -2560,7 +2721,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -2583,7 +2744,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -2606,7 +2767,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -2629,7 +2790,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -2652,7 +2813,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -2675,7 +2836,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -2698,7 +2859,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -2721,7 +2882,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -2744,7 +2905,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -2767,7 +2928,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -2790,7 +2951,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -2813,7 +2974,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -2836,7 +2997,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -2859,7 +3020,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -2882,7 +3043,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -2905,7 +3066,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -2926,6 +3087,167 @@
       </c>
       <c r="G53" s="9">
         <v>115</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>110</v>
+      </c>
+      <c r="F54" s="9">
+        <v>117</v>
+      </c>
+      <c r="G54" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>110</v>
+      </c>
+      <c r="F55" s="9">
+        <v>117</v>
+      </c>
+      <c r="G55" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>110</v>
+      </c>
+      <c r="F56" s="9">
+        <v>117</v>
+      </c>
+      <c r="G56" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>110</v>
+      </c>
+      <c r="F57" s="9">
+        <v>117</v>
+      </c>
+      <c r="G57" s="9">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>105</v>
+      </c>
+      <c r="F58" s="9">
+        <v>112</v>
+      </c>
+      <c r="G58" s="9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>105</v>
+      </c>
+      <c r="F59" s="9">
+        <v>112</v>
+      </c>
+      <c r="G59" s="9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>105</v>
+      </c>
+      <c r="F60" s="9">
+        <v>112</v>
+      </c>
+      <c r="G60" s="9">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2936,19 +3258,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C6C0178-E414-47B2-A630-84DA7232A61F}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2971,7 +3293,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -2994,7 +3316,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -3017,7 +3339,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -3040,7 +3362,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -3063,7 +3385,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -3086,7 +3408,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -3109,7 +3431,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -3132,7 +3454,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -3155,7 +3477,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -3178,7 +3500,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -3201,7 +3523,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -3224,7 +3546,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -3247,7 +3569,7 @@
         <v>62.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -3270,7 +3592,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -3293,7 +3615,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -3316,7 +3638,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -3339,7 +3661,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -3362,7 +3684,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -3385,7 +3707,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -3408,7 +3730,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -3431,7 +3753,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -3454,7 +3776,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -3477,7 +3799,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -3500,7 +3822,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -3523,7 +3845,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -3546,7 +3868,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -3569,7 +3891,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -3592,7 +3914,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -3615,7 +3937,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -3638,7 +3960,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -3661,7 +3983,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -3684,7 +4006,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -3707,7 +4029,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -3730,7 +4052,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -3753,7 +4075,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -3776,7 +4098,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -3799,7 +4121,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -3822,7 +4144,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -3845,7 +4167,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -3868,7 +4190,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -3891,7 +4213,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -3914,7 +4236,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -3937,7 +4259,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -3960,7 +4282,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -3983,7 +4305,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -4006,7 +4328,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -4029,7 +4351,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -4052,7 +4374,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -4075,7 +4397,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -4098,7 +4420,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -4121,7 +4443,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -4144,7 +4466,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -4164,6 +4486,167 @@
         <v>197</v>
       </c>
       <c r="G53" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>193</v>
+      </c>
+      <c r="F54" s="9">
+        <v>197</v>
+      </c>
+      <c r="G54" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>193</v>
+      </c>
+      <c r="F55" s="9">
+        <v>197</v>
+      </c>
+      <c r="G55" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>193</v>
+      </c>
+      <c r="F56" s="9">
+        <v>197</v>
+      </c>
+      <c r="G56" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>193</v>
+      </c>
+      <c r="F57" s="9">
+        <v>197</v>
+      </c>
+      <c r="G57" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>193</v>
+      </c>
+      <c r="F58" s="9">
+        <v>197</v>
+      </c>
+      <c r="G58" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>193</v>
+      </c>
+      <c r="F59" s="9">
+        <v>197</v>
+      </c>
+      <c r="G59" s="9">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>193</v>
+      </c>
+      <c r="F60" s="9">
+        <v>197</v>
+      </c>
+      <c r="G60" s="9">
         <v>195</v>
       </c>
     </row>
@@ -4175,20 +4658,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACE21688-DF7E-4F8C-887E-342649A09FB0}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4211,7 +4694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -4234,7 +4717,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -4257,7 +4740,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -4280,7 +4763,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -4303,7 +4786,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -4326,7 +4809,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -4349,7 +4832,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -4372,7 +4855,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -4395,7 +4878,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -4418,7 +4901,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -4441,7 +4924,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -4464,7 +4947,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -4487,7 +4970,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -4510,7 +4993,7 @@
         <v>23.8</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -4533,7 +5016,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -4556,7 +5039,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -4579,7 +5062,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -4602,7 +5085,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -4625,7 +5108,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -4648,7 +5131,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -4671,7 +5154,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -4694,7 +5177,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -4717,7 +5200,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -4740,7 +5223,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -4763,7 +5246,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -4786,7 +5269,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -4809,7 +5292,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -4832,7 +5315,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -4855,7 +5338,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -4878,7 +5361,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -4901,7 +5384,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -4924,7 +5407,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -4947,7 +5430,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -4970,7 +5453,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -4993,7 +5476,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -5016,7 +5499,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -5039,7 +5522,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -5062,7 +5545,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -5085,7 +5568,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -5108,7 +5591,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -5131,7 +5614,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -5154,7 +5637,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -5177,7 +5660,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -5200,7 +5683,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -5223,7 +5706,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -5246,7 +5729,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -5269,7 +5752,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -5292,7 +5775,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -5315,7 +5798,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -5338,7 +5821,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -5361,7 +5844,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -5384,7 +5867,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -5405,6 +5888,167 @@
       </c>
       <c r="G53" s="9">
         <v>75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F54" s="9">
+        <v>76</v>
+      </c>
+      <c r="G54" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F55" s="9">
+        <v>76</v>
+      </c>
+      <c r="G55" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F56" s="9">
+        <v>76</v>
+      </c>
+      <c r="G56" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>73.5</v>
+      </c>
+      <c r="F57" s="9">
+        <v>76</v>
+      </c>
+      <c r="G57" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>71.5</v>
+      </c>
+      <c r="F58" s="9">
+        <v>74</v>
+      </c>
+      <c r="G58" s="9">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>71.5</v>
+      </c>
+      <c r="F59" s="9">
+        <v>74</v>
+      </c>
+      <c r="G59" s="9">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>71.5</v>
+      </c>
+      <c r="F60" s="9">
+        <v>74</v>
+      </c>
+      <c r="G60" s="9">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -5415,19 +6059,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{075E49D7-A50C-4EF3-8D98-3E3352C23834}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5450,7 +6094,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -5473,7 +6117,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -5496,7 +6140,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -5519,7 +6163,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -5542,7 +6186,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -5565,7 +6209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -5588,7 +6232,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -5611,7 +6255,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -5634,7 +6278,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -5657,7 +6301,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -5680,7 +6324,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -5703,7 +6347,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -5726,7 +6370,7 @@
         <v>36.4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -5749,7 +6393,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -5772,7 +6416,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -5795,7 +6439,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -5818,7 +6462,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -5841,7 +6485,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -5864,7 +6508,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -5887,7 +6531,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -5910,7 +6554,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -5933,7 +6577,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -5956,7 +6600,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -5979,7 +6623,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -6002,7 +6646,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -6025,7 +6669,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -6048,7 +6692,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -6071,7 +6715,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -6094,7 +6738,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -6117,7 +6761,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -6140,7 +6784,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -6163,7 +6807,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -6186,7 +6830,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -6209,7 +6853,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -6232,7 +6876,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -6255,7 +6899,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -6278,7 +6922,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -6301,7 +6945,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -6324,7 +6968,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -6347,7 +6991,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -6370,7 +7014,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -6393,7 +7037,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -6416,7 +7060,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -6439,7 +7083,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -6462,7 +7106,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -6485,7 +7129,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -6508,7 +7152,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -6531,7 +7175,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -6554,7 +7198,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -6577,7 +7221,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -6600,7 +7244,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -6623,7 +7267,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -6644,6 +7288,167 @@
       </c>
       <c r="G53" s="9">
         <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F54" s="9">
+        <v>131</v>
+      </c>
+      <c r="G54" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F55" s="9">
+        <v>131</v>
+      </c>
+      <c r="G55" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F56" s="9">
+        <v>131</v>
+      </c>
+      <c r="G56" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>125.5</v>
+      </c>
+      <c r="F57" s="9">
+        <v>131</v>
+      </c>
+      <c r="G57" s="9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>122.5</v>
+      </c>
+      <c r="F58" s="9">
+        <v>128</v>
+      </c>
+      <c r="G58" s="9">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>122.5</v>
+      </c>
+      <c r="F59" s="9">
+        <v>128</v>
+      </c>
+      <c r="G59" s="9">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>122.5</v>
+      </c>
+      <c r="F60" s="9">
+        <v>128</v>
+      </c>
+      <c r="G60" s="9">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -6654,19 +7459,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18515E64-A7B9-4EA8-8571-9A16CD6B2FD3}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6689,7 +7494,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -6712,7 +7517,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -6735,7 +7540,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -6758,7 +7563,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -6781,7 +7586,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -6804,7 +7609,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -6827,7 +7632,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -6850,7 +7655,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -6873,7 +7678,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -6896,7 +7701,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -6919,7 +7724,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -6942,7 +7747,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -6965,7 +7770,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -6988,7 +7793,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -7011,7 +7816,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -7034,7 +7839,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -7057,7 +7862,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -7080,7 +7885,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -7103,7 +7908,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -7126,7 +7931,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -7149,7 +7954,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -7172,7 +7977,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -7195,7 +8000,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -7218,7 +8023,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -7241,7 +8046,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -7264,7 +8069,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -7287,7 +8092,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -7310,7 +8115,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -7333,7 +8138,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -7356,7 +8161,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -7379,7 +8184,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -7402,7 +8207,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -7425,7 +8230,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -7448,7 +8253,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -7471,7 +8276,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -7494,7 +8299,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -7517,7 +8322,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -7540,7 +8345,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -7563,7 +8368,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -7586,7 +8391,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -7609,7 +8414,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -7632,7 +8437,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -7655,7 +8460,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -7678,7 +8483,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -7701,7 +8506,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -7724,7 +8529,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -7747,7 +8552,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -7770,7 +8575,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -7793,7 +8598,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -7816,7 +8621,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -7839,7 +8644,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -7862,7 +8667,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -7882,6 +8687,167 @@
         <v>202</v>
       </c>
       <c r="G53" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>199</v>
+      </c>
+      <c r="F54" s="9">
+        <v>202</v>
+      </c>
+      <c r="G54" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>199</v>
+      </c>
+      <c r="F55" s="9">
+        <v>202</v>
+      </c>
+      <c r="G55" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>199</v>
+      </c>
+      <c r="F56" s="9">
+        <v>202</v>
+      </c>
+      <c r="G56" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>199</v>
+      </c>
+      <c r="F57" s="9">
+        <v>202</v>
+      </c>
+      <c r="G57" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>199</v>
+      </c>
+      <c r="F58" s="9">
+        <v>202</v>
+      </c>
+      <c r="G58" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>199</v>
+      </c>
+      <c r="F59" s="9">
+        <v>202</v>
+      </c>
+      <c r="G59" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>199</v>
+      </c>
+      <c r="F60" s="9">
+        <v>202</v>
+      </c>
+      <c r="G60" s="9">
         <v>200</v>
       </c>
     </row>
@@ -7893,19 +8859,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8286ED8B-68EC-4D79-8787-976F03BA0C32}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="6.69921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="6.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7928,7 +8894,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -7951,7 +8917,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -7974,7 +8940,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -7997,7 +8963,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -8020,7 +8986,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -8043,7 +9009,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -8066,7 +9032,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -8089,7 +9055,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -8112,7 +9078,7 @@
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -8135,7 +9101,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -8158,7 +9124,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -8181,7 +9147,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -8204,7 +9170,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -8227,7 +9193,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -8250,7 +9216,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -8273,7 +9239,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -8296,7 +9262,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -8319,7 +9285,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -8342,7 +9308,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -8365,7 +9331,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -8388,7 +9354,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -8411,7 +9377,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -8434,7 +9400,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -8457,7 +9423,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -8480,7 +9446,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -8503,7 +9469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -8526,7 +9492,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -8549,7 +9515,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -8572,7 +9538,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -8595,7 +9561,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -8618,7 +9584,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -8641,7 +9607,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -8664,7 +9630,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -8687,7 +9653,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -8710,7 +9676,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -8733,7 +9699,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -8756,7 +9722,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -8779,7 +9745,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -8802,7 +9768,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -8825,7 +9791,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -8848,7 +9814,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -8871,7 +9837,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -8894,7 +9860,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -8917,7 +9883,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -8940,7 +9906,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -8963,7 +9929,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -8986,7 +9952,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -9009,7 +9975,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -9032,7 +9998,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -9055,7 +10021,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -9078,7 +10044,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -9101,7 +10067,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -9121,6 +10087,167 @@
         <v>144</v>
       </c>
       <c r="G53" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="9">
+        <v>140</v>
+      </c>
+      <c r="F54" s="9">
+        <v>144</v>
+      </c>
+      <c r="G54" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="9">
+        <v>140</v>
+      </c>
+      <c r="F55" s="9">
+        <v>144</v>
+      </c>
+      <c r="G55" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="9">
+        <v>140</v>
+      </c>
+      <c r="F56" s="9">
+        <v>144</v>
+      </c>
+      <c r="G56" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="9">
+        <v>140</v>
+      </c>
+      <c r="F57" s="9">
+        <v>144</v>
+      </c>
+      <c r="G57" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="9">
+        <v>140</v>
+      </c>
+      <c r="F58" s="9">
+        <v>144</v>
+      </c>
+      <c r="G58" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="9">
+        <v>140</v>
+      </c>
+      <c r="F59" s="9">
+        <v>144</v>
+      </c>
+      <c r="G59" s="9">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="9">
+        <v>140</v>
+      </c>
+      <c r="F60" s="9">
+        <v>144</v>
+      </c>
+      <c r="G60" s="9">
         <v>142</v>
       </c>
     </row>
@@ -9132,20 +10259,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62752974-E8DF-439D-ACF9-ECD10A65F3F8}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.8984375" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.3984375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9168,7 +10295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -9191,7 +10318,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -9214,7 +10341,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -9237,7 +10364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -9260,7 +10387,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -9283,7 +10410,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -9306,7 +10433,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -9329,7 +10456,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -9352,7 +10479,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -9375,7 +10502,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -9398,7 +10525,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -9421,7 +10548,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -9444,7 +10571,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -9467,7 +10594,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -9490,7 +10617,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -9513,7 +10640,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -9536,7 +10663,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -9559,7 +10686,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -9582,7 +10709,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -9605,7 +10732,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -9628,7 +10755,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -9651,7 +10778,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -9674,7 +10801,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -9697,7 +10824,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -9720,7 +10847,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -9743,7 +10870,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -9766,7 +10893,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -9789,7 +10916,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -9812,7 +10939,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -9835,7 +10962,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -9858,7 +10985,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -9881,7 +11008,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -9904,7 +11031,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -9927,7 +11054,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -9950,7 +11077,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -9973,7 +11100,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -9996,7 +11123,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -10019,7 +11146,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -10042,7 +11169,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -10065,7 +11192,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -10088,7 +11215,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -10111,7 +11238,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -10134,7 +11261,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -10157,7 +11284,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -10180,7 +11307,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -10203,7 +11330,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -10226,7 +11353,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -10249,7 +11376,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -10272,7 +11399,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -10295,7 +11422,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -10318,7 +11445,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -10341,7 +11468,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -10361,6 +11488,167 @@
         <v>231</v>
       </c>
       <c r="G53" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="12">
+        <v>228</v>
+      </c>
+      <c r="F54" s="12">
+        <v>231</v>
+      </c>
+      <c r="G54" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="12">
+        <v>228</v>
+      </c>
+      <c r="F55" s="12">
+        <v>231</v>
+      </c>
+      <c r="G55" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="12">
+        <v>228</v>
+      </c>
+      <c r="F56" s="12">
+        <v>231</v>
+      </c>
+      <c r="G56" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="12">
+        <v>228</v>
+      </c>
+      <c r="F57" s="12">
+        <v>231</v>
+      </c>
+      <c r="G57" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="12">
+        <v>228</v>
+      </c>
+      <c r="F58" s="12">
+        <v>231</v>
+      </c>
+      <c r="G58" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="12">
+        <v>228</v>
+      </c>
+      <c r="F59" s="12">
+        <v>231</v>
+      </c>
+      <c r="G59" s="12">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="12">
+        <v>228</v>
+      </c>
+      <c r="F60" s="12">
+        <v>231</v>
+      </c>
+      <c r="G60" s="12">
         <v>230</v>
       </c>
     </row>
@@ -10372,19 +11660,19 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A9F2B4-31D6-4C55-BAC0-7D448A9FC534}">
-  <dimension ref="A1:G53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.796875" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.59765625" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="7.59765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="7.6640625" style="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10407,7 +11695,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45860</v>
       </c>
@@ -10430,7 +11718,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45867</v>
       </c>
@@ -10453,7 +11741,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45874</v>
       </c>
@@ -10476,7 +11764,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45881</v>
       </c>
@@ -10499,7 +11787,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45888</v>
       </c>
@@ -10522,7 +11810,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45895</v>
       </c>
@@ -10545,7 +11833,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45902</v>
       </c>
@@ -10568,7 +11856,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45909</v>
       </c>
@@ -10591,7 +11879,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>45916</v>
       </c>
@@ -10614,7 +11902,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>45923</v>
       </c>
@@ -10637,7 +11925,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>45930</v>
       </c>
@@ -10660,7 +11948,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>45944</v>
       </c>
@@ -10683,7 +11971,7 @@
         <v>126.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45951</v>
       </c>
@@ -10706,7 +11994,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45958</v>
       </c>
@@ -10729,7 +12017,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45965</v>
       </c>
@@ -10752,7 +12040,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45972</v>
       </c>
@@ -10775,7 +12063,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45979</v>
       </c>
@@ -10798,7 +12086,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45986</v>
       </c>
@@ -10821,7 +12109,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45993</v>
       </c>
@@ -10844,7 +12132,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>46000</v>
       </c>
@@ -10867,7 +12155,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>46007</v>
       </c>
@@ -10890,7 +12178,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>46014</v>
       </c>
@@ -10913,7 +12201,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>46021</v>
       </c>
@@ -10936,7 +12224,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>46028</v>
       </c>
@@ -10959,7 +12247,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="10">
         <v>46035</v>
       </c>
@@ -10982,7 +12270,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="10">
         <v>46042</v>
       </c>
@@ -11005,7 +12293,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>46049</v>
       </c>
@@ -11028,7 +12316,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="10">
         <v>46056</v>
       </c>
@@ -11051,7 +12339,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="10">
         <v>46063</v>
       </c>
@@ -11074,7 +12362,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="10">
         <v>46077</v>
       </c>
@@ -11097,7 +12385,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="10">
         <v>46084</v>
       </c>
@@ -11120,7 +12408,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="10">
         <v>46091</v>
       </c>
@@ -11143,7 +12431,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="10">
         <v>46098</v>
       </c>
@@ -11166,7 +12454,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="10">
         <v>46105</v>
       </c>
@@ -11189,7 +12477,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="10">
         <v>46112</v>
       </c>
@@ -11212,7 +12500,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="10">
         <v>46119</v>
       </c>
@@ -11235,7 +12523,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="10">
         <v>46126</v>
       </c>
@@ -11258,7 +12546,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="10">
         <v>46133</v>
       </c>
@@ -11281,7 +12569,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="10">
         <v>46140</v>
       </c>
@@ -11304,7 +12592,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="10">
         <v>46154</v>
       </c>
@@ -11327,7 +12615,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="10">
         <v>46161</v>
       </c>
@@ -11350,7 +12638,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
         <v>46168</v>
       </c>
@@ -11373,7 +12661,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="10">
         <v>46175</v>
       </c>
@@ -11396,7 +12684,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="10">
         <v>46182</v>
       </c>
@@ -11419,7 +12707,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="10">
         <v>46189</v>
       </c>
@@ -11442,7 +12730,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="10">
         <v>46196</v>
       </c>
@@ -11465,7 +12753,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="10">
         <v>46203</v>
       </c>
@@ -11488,7 +12776,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="10">
         <v>46210</v>
       </c>
@@ -11511,7 +12799,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="10">
         <v>46217</v>
       </c>
@@ -11534,7 +12822,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="10">
         <v>46224</v>
       </c>
@@ -11557,7 +12845,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="10">
         <v>46231</v>
       </c>
@@ -11580,7 +12868,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="10">
         <v>46238</v>
       </c>
@@ -11600,6 +12888,167 @@
         <v>405</v>
       </c>
       <c r="G53" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="B54" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C54" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="14">
+        <v>398</v>
+      </c>
+      <c r="F54" s="14">
+        <v>405</v>
+      </c>
+      <c r="G54" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="B55" s="10">
+        <v>46252</v>
+      </c>
+      <c r="C55" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="14">
+        <v>398</v>
+      </c>
+      <c r="F55" s="14">
+        <v>405</v>
+      </c>
+      <c r="G55" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="B56" s="10">
+        <v>46259</v>
+      </c>
+      <c r="C56" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="14">
+        <v>398</v>
+      </c>
+      <c r="F56" s="14">
+        <v>405</v>
+      </c>
+      <c r="G56" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="10">
+        <v>46266</v>
+      </c>
+      <c r="C57" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="14">
+        <v>398</v>
+      </c>
+      <c r="F57" s="14">
+        <v>405</v>
+      </c>
+      <c r="G57" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="B58" s="10">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="14">
+        <v>398</v>
+      </c>
+      <c r="F58" s="14">
+        <v>405</v>
+      </c>
+      <c r="G58" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="B59" s="10">
+        <v>46280</v>
+      </c>
+      <c r="C59" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="14">
+        <v>398</v>
+      </c>
+      <c r="F59" s="14">
+        <v>405</v>
+      </c>
+      <c r="G59" s="14">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B60" s="10">
+        <v>46287</v>
+      </c>
+      <c r="C60" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="14">
+        <v>398</v>
+      </c>
+      <c r="F60" s="14">
+        <v>405</v>
+      </c>
+      <c r="G60" s="14">
         <v>400</v>
       </c>
     </row>
